--- a/Localization/LangEverydayJapanese.xlsx
+++ b/Localization/LangEverydayJapanese.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kimkihoon/Work/Project/EverydayJapanese/Localization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E9391E-9E4A-4F49-8ADF-9D130876F1E8}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B101ACA-9FC7-4C40-9082-68119AD2EC39}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37140" yWindow="500" windowWidth="33600" windowHeight="19720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37440" yWindow="640" windowWidth="33600" windowHeight="19720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="270">
   <si>
     <t>String_Index</t>
   </si>
@@ -892,6 +892,86 @@
   </si>
   <si>
     <t>test_result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>app_widget_description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">매일 매일 앱위젯으로 단어를 공부해 보세요 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>You can study with app widget everyday.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>common_setting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Setting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>everyday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 hour</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>one_hour</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>암기할 부분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단어 변경 주기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>part to memorize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frequency of word change</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frequency_word_change</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>part_memorize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>즐겨찾기에 등록된 단어가 없어요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>There are no words registered in favorites</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>no_words_registered_favorites</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2184,7 +2264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F245"/>
+  <dimension ref="A1:F246"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52" style="4" customWidth="1"/>
@@ -2391,7 +2471,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
         <v>98</v>
       </c>
@@ -2403,7 +2483,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
         <v>101</v>
       </c>
@@ -2415,7 +2495,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
         <v>100</v>
       </c>
@@ -2427,7 +2507,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
         <v>103</v>
       </c>
@@ -2439,7 +2519,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
         <v>104</v>
       </c>
@@ -2451,7 +2531,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
         <v>102</v>
       </c>
@@ -2463,7 +2543,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
         <v>111</v>
       </c>
@@ -2475,7 +2555,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
         <v>120</v>
       </c>
@@ -2487,7 +2567,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
         <v>121</v>
       </c>
@@ -2499,7 +2579,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
         <v>138</v>
       </c>
@@ -2511,7 +2591,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
         <v>143</v>
       </c>
@@ -2523,7 +2603,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
         <v>144</v>
       </c>
@@ -2535,7 +2615,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
         <v>175</v>
       </c>
@@ -2547,789 +2627,831 @@
         <v>173</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="6"/>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="9" t="s">
+      <c r="C30" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="9" t="s">
+      <c r="B32" s="10"/>
+      <c r="C32" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="D31" s="10"/>
-    </row>
-    <row r="32" spans="1:6" ht="16">
-      <c r="A32" s="6" t="s">
+      <c r="D32" s="10"/>
+    </row>
+    <row r="33" spans="1:6" ht="16">
+      <c r="A33" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6" t="s">
+      <c r="B33" s="6"/>
+      <c r="C33" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D33" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="7" t="s">
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="7" t="s">
-        <v>60</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="7" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="7" t="s">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B36" s="8"/>
       <c r="C36" s="7" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="7" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B38" s="8"/>
       <c r="C38" s="7" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B40" s="8"/>
       <c r="C40" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B42" s="8"/>
       <c r="C42" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43" s="8"/>
+      <c r="C43" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D43" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="16">
-      <c r="A43" s="6" t="s">
+    <row r="44" spans="1:6" ht="16">
+      <c r="A44" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="16">
-      <c r="A44" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="16">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="16">
       <c r="A45" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="16">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="16">
       <c r="A46" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="16">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="16">
       <c r="A47" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="16">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="16">
       <c r="A48" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="16">
+      <c r="A49" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D49" s="6" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="1" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1" t="s">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="1" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>153</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="B61" s="6"/>
+      <c r="C61" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="16">
-      <c r="A61" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="16">
       <c r="A62" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="16">
       <c r="A63" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="16">
       <c r="A64" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="16">
+      <c r="A65" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="D65" s="6" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-    </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="9" t="s">
+      <c r="A66" s="6"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B66" s="10"/>
-      <c r="C66" s="9" t="s">
+      <c r="B67" s="10"/>
+      <c r="C67" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D66" s="10"/>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B67" s="1"/>
-      <c r="C67" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>180</v>
-      </c>
+      <c r="D67" s="10"/>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D70" s="1" t="s">
         <v>186</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="16">
-      <c r="A70" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="16">
       <c r="A71" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="16">
+      <c r="A72" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D71" s="6" t="s">
+      <c r="D72" s="6" t="s">
         <v>191</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B72" s="6"/>
-      <c r="C72" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="1" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B74" s="6"/>
       <c r="C74" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="1" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="B75" s="6"/>
       <c r="C75" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B76" s="6"/>
       <c r="C76" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B77" s="6"/>
       <c r="C77" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B78" s="6"/>
       <c r="C78" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B79" s="6"/>
       <c r="C79" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B80" s="6"/>
       <c r="C80" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="B81" s="6"/>
       <c r="C81" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B82" s="6"/>
       <c r="C82" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B91" s="6"/>
+      <c r="C91" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D91" s="1" t="s">
         <v>226</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="16">
-      <c r="A91" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="B91" s="6"/>
-      <c r="C91" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="16">
       <c r="A92" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="16">
+      <c r="A93" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="D92" s="6" t="s">
+      <c r="D93" s="6" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="6"/>
+    <row r="94" spans="1:4" ht="16">
+      <c r="A94" s="6" t="s">
+        <v>250</v>
+      </c>
       <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" s="6"/>
+      <c r="C94" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="16">
+      <c r="A95" s="6" t="s">
+        <v>258</v>
+      </c>
       <c r="B95" s="6"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" s="6"/>
+      <c r="C95" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="16">
+      <c r="A96" s="6" t="s">
+        <v>260</v>
+      </c>
       <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="6"/>
+      <c r="C96" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="16">
+      <c r="A97" s="6" t="s">
+        <v>266</v>
+      </c>
       <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="6"/>
+      <c r="C97" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="16">
+      <c r="A98" s="6" t="s">
+        <v>265</v>
+      </c>
       <c r="B98" s="6"/>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6"/>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="6"/>
+      <c r="C98" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="16">
+      <c r="A99" s="6" t="s">
+        <v>269</v>
+      </c>
       <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
+      <c r="C99" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="6"/>
@@ -4206,6 +4328,12 @@
       <c r="B245" s="6"/>
       <c r="C245" s="6"/>
       <c r="D245" s="6"/>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="6"/>
+      <c r="B246" s="6"/>
+      <c r="C246" s="6"/>
+      <c r="D246" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
